--- a/California_ECE_District_Contacts_2026-04-01.xlsx
+++ b/California_ECE_District_Contacts_2026-04-01.xlsx
@@ -463,15 +463,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q97"/>
+  <dimension ref="A1:Q202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="57" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
@@ -479,7 +479,7 @@
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="29" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="37" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
@@ -7215,6 +7215,6596 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Alhambra Unified</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>0600153</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>26500</v>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>1515 West Mission Road, Alhambra, CA 91803</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr"/>
+      <c r="H98" s="3" t="inlineStr"/>
+      <c r="I98" s="3" t="inlineStr"/>
+      <c r="J98" s="3" t="inlineStr"/>
+      <c r="K98" s="3" t="inlineStr"/>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>(626) 943-3000</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>Creative Curriculum by Teaching Strategies</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr"/>
+      <c r="O98" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Curriculum | Creative Curriculum confirmed in use | ausd.us | 2024</t>
+        </is>
+      </c>
+      <c r="P98" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ausd.us/departments/educational-services/early-childhood-education</t>
+        </is>
+      </c>
+      <c r="Q98" s="4" t="inlineStr">
+        <is>
+          <t>ECE director name not confirmed publicly. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>Burbank Unified</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>0600254</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>1900 West Olive Avenue, Burbank, CA 91506</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="7" t="inlineStr"/>
+      <c r="I99" s="7" t="inlineStr"/>
+      <c r="J99" s="7" t="inlineStr"/>
+      <c r="K99" s="7" t="inlineStr"/>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>(818) 729-4400</t>
+        </is>
+      </c>
+      <c r="M99" s="7" t="inlineStr">
+        <is>
+          <t>Creative Curriculum by Teaching Strategies</t>
+        </is>
+      </c>
+      <c r="N99" s="7" t="inlineStr"/>
+      <c r="O99" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Curriculum | Creative Curriculum confirmed in use | burbankusd.org | 2024</t>
+        </is>
+      </c>
+      <c r="P99" s="7" t="inlineStr">
+        <is>
+          <t>https://www.burbankusd.org/departments/educational-services/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q99" s="8" t="inlineStr">
+        <is>
+          <t>ECE director name not confirmed publicly. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>Paramount Unified</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>0600407</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>16800</v>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>15110 California Avenue, Paramount, CA 90723</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr"/>
+      <c r="H100" s="3" t="inlineStr"/>
+      <c r="I100" s="3" t="inlineStr"/>
+      <c r="J100" s="3" t="inlineStr"/>
+      <c r="K100" s="3" t="inlineStr"/>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>(562) 602-6000</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>Head Start; California State Preschool Program (CSPP)</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr"/>
+      <c r="O100" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Program | Head Start and CSPP programs in operation | paramount.k12.ca.us | 2024</t>
+        </is>
+      </c>
+      <c r="P100" s="3" t="inlineStr">
+        <is>
+          <t>https://www.paramount.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q100" s="4" t="inlineStr">
+        <is>
+          <t>ECE director name not confirmed publicly. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>Inglewood Unified</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>0600330</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="n">
+        <v>13200</v>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>401 South Inglewood Avenue, Inglewood, CA 90301</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>Joanna</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>Clifton</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="inlineStr">
+        <is>
+          <t>Director, Child Development Center</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr"/>
+      <c r="K101" s="7" t="inlineStr"/>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>(310) 419-2691</t>
+        </is>
+      </c>
+      <c r="M101" s="7" t="inlineStr">
+        <is>
+          <t>California DOE-aligned curriculum; CSPP</t>
+        </is>
+      </c>
+      <c r="N101" s="7" t="inlineStr"/>
+      <c r="O101" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P101" s="7" t="inlineStr">
+        <is>
+          <t>https://cdc.inglewoodusd.com/</t>
+        </is>
+      </c>
+      <c r="Q101" s="8" t="inlineStr">
+        <is>
+          <t>Joanna Clifton confirmed as Director, Child Development Center. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>Lynwood Unified</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>0622530</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>12500</v>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>11321 Bullis Road, Lynwood, CA 90262</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr"/>
+      <c r="H102" s="3" t="inlineStr"/>
+      <c r="I102" s="3" t="inlineStr"/>
+      <c r="J102" s="3" t="inlineStr"/>
+      <c r="K102" s="3" t="inlineStr"/>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>(310) 886-1600</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr"/>
+      <c r="O102" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+QRIS | ECE program earned Tier 4 quality rating at 11 of 12 sites; Lugo Elementary rated Tier 5 | mylusd.org | 2024</t>
+        </is>
+      </c>
+      <c r="P102" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mylusd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q102" s="4" t="inlineStr">
+        <is>
+          <t>High QRIS ratings across sites — signal of program quality focus. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>Azusa Unified</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>0603450</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>546 South Citrus Avenue, Azusa, CA 91702</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr"/>
+      <c r="H103" s="7" t="inlineStr"/>
+      <c r="I103" s="7" t="inlineStr"/>
+      <c r="J103" s="7" t="inlineStr"/>
+      <c r="K103" s="7" t="inlineStr"/>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>(626) 858-6000</t>
+        </is>
+      </c>
+      <c r="M103" s="7" t="inlineStr">
+        <is>
+          <t>California State Preschool Program (CSPP)</t>
+        </is>
+      </c>
+      <c r="N103" s="7" t="inlineStr"/>
+      <c r="O103" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Expansion | Dual Language Immersion PreK in Mandarin and Spanish expanding; Hodge Elementary DLI opening Fall 2025 | azusa.org | 2025</t>
+        </is>
+      </c>
+      <c r="P103" s="7" t="inlineStr">
+        <is>
+          <t>https://www.azusa.org/programs/early-childhood-education</t>
+        </is>
+      </c>
+      <c r="Q103" s="8" t="inlineStr">
+        <is>
+          <t>DLI PreK expansion is a strong buying signal. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Covina-Valley Unified</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>0609780</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>10500</v>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>519 East Badillo Street, Covina, CA 91723</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr"/>
+      <c r="H104" s="3" t="inlineStr"/>
+      <c r="I104" s="3" t="inlineStr"/>
+      <c r="J104" s="3" t="inlineStr"/>
+      <c r="K104" s="3" t="inlineStr"/>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>(626) 974-7000</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; TK aligned with CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr"/>
+      <c r="O104" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P104" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cvusd.us/departments/educational-services/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q104" s="4" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>West Covina Unified</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>0641760</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="n">
+        <v>9600</v>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>1717 West Merced Avenue, West Covina, CA 91790</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr"/>
+      <c r="H105" s="7" t="inlineStr"/>
+      <c r="I105" s="7" t="inlineStr"/>
+      <c r="J105" s="7" t="inlineStr"/>
+      <c r="K105" s="7" t="inlineStr"/>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>(626) 939-4600</t>
+        </is>
+      </c>
+      <c r="M105" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; developmentally appropriate play-based curriculum</t>
+        </is>
+      </c>
+      <c r="N105" s="7" t="inlineStr"/>
+      <c r="O105" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P105" s="7" t="inlineStr">
+        <is>
+          <t>https://www.wcusd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q105" s="8" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>El Monte City School District</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>0612690</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>10500</v>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>3540 Lexington Avenue, El Monte, CA 91731</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr"/>
+      <c r="H106" s="3" t="inlineStr"/>
+      <c r="I106" s="3" t="inlineStr"/>
+      <c r="J106" s="3" t="inlineStr"/>
+      <c r="K106" s="3" t="inlineStr"/>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>(626) 453-3700</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; TK Kinder Readiness Academy</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr"/>
+      <c r="O106" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Program | TK Kinder Readiness Academy offering free summer transition programming | emcsd.org | 2024</t>
+        </is>
+      </c>
+      <c r="P106" s="3" t="inlineStr">
+        <is>
+          <t>https://www.emcsd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q106" s="4" t="inlineStr">
+        <is>
+          <t>Elementary district (PK-8). ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>Santa Monica-Malibu Unified</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>0635340</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>1651 16th Street, Santa Monica, CA 90404</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr"/>
+      <c r="H107" s="7" t="inlineStr"/>
+      <c r="I107" s="7" t="inlineStr"/>
+      <c r="J107" s="7" t="inlineStr"/>
+      <c r="K107" s="7" t="inlineStr"/>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>(310) 450-8338</t>
+        </is>
+      </c>
+      <c r="M107" s="7" t="inlineStr">
+        <is>
+          <t>Play-based, developmentally appropriate; Bridges TK Program</t>
+        </is>
+      </c>
+      <c r="N107" s="7" t="inlineStr"/>
+      <c r="O107" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Strategic | Neighborhood Preschools (Seaside Preschool) and Bridges TK Program launched as strategic initiatives | smmusd.org | 2024</t>
+        </is>
+      </c>
+      <c r="P107" s="7" t="inlineStr">
+        <is>
+          <t>https://www.smmusd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q107" s="8" t="inlineStr">
+        <is>
+          <t>Active strategic investment in early learning programs. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>Arcadia Unified</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>0602370</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>9400</v>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>150 South Second Avenue, Arcadia, CA 91006</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr"/>
+      <c r="H108" s="3" t="inlineStr"/>
+      <c r="I108" s="3" t="inlineStr"/>
+      <c r="J108" s="3" t="inlineStr"/>
+      <c r="K108" s="3" t="inlineStr"/>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>(626) 821-8300</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; TK aligned with CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr"/>
+      <c r="O108" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P108" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ausd.net/departments/educational-services/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q108" s="4" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>Palos Verdes Peninsula Unified</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>0629280</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>375 Via Almar, Palos Verdes Estates, CA 90274</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr"/>
+      <c r="H109" s="7" t="inlineStr"/>
+      <c r="I109" s="7" t="inlineStr"/>
+      <c r="J109" s="7" t="inlineStr"/>
+      <c r="K109" s="7" t="inlineStr"/>
+      <c r="L109" s="7" t="inlineStr">
+        <is>
+          <t>(310) 378-9966</t>
+        </is>
+      </c>
+      <c r="M109" s="7" t="inlineStr">
+        <is>
+          <t>Developmentally appropriate, literacy and math focused TK</t>
+        </is>
+      </c>
+      <c r="N109" s="7" t="inlineStr"/>
+      <c r="O109" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P109" s="7" t="inlineStr">
+        <is>
+          <t>https://www.pvpusd.net/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q109" s="8" t="inlineStr">
+        <is>
+          <t>Affluent district; high TK demand. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>Culver City Unified</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>0610380</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>4034 Irving Place, Culver City, CA 90232</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr"/>
+      <c r="H110" s="3" t="inlineStr"/>
+      <c r="I110" s="3" t="inlineStr"/>
+      <c r="J110" s="3" t="inlineStr"/>
+      <c r="K110" s="3" t="inlineStr"/>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>(310) 842-4220</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>Developmentally appropriate, individualized early childhood curriculum</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr"/>
+      <c r="O110" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P110" s="3" t="inlineStr">
+        <is>
+          <t>https://ocd.ccusd.org/</t>
+        </is>
+      </c>
+      <c r="Q110" s="4" t="inlineStr">
+        <is>
+          <t>Child Development Program. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>Las Virgenes Unified</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>0621090</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="n">
+        <v>8700</v>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>4111 Las Virgenes Road, Calabasas, CA 91302</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>Valerie</t>
+        </is>
+      </c>
+      <c r="H111" s="7" t="inlineStr">
+        <is>
+          <t>Louthian</t>
+        </is>
+      </c>
+      <c r="I111" s="7" t="inlineStr">
+        <is>
+          <t>Program Coordinator, Early Childhood Programs</t>
+        </is>
+      </c>
+      <c r="J111" s="7" t="inlineStr"/>
+      <c r="K111" s="7" t="inlineStr"/>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>(818) 880-4000</t>
+        </is>
+      </c>
+      <c r="M111" s="7" t="inlineStr">
+        <is>
+          <t>Play-based, CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N111" s="7" t="inlineStr"/>
+      <c r="O111" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P111" s="7" t="inlineStr">
+        <is>
+          <t>https://www.lvusd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q111" s="8" t="inlineStr">
+        <is>
+          <t>Valerie Louthian confirmed as Program Coordinator. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>Glendora Unified</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>0615360</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>500 North Loraine Avenue, Glendora, CA 91741</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr"/>
+      <c r="H112" s="3" t="inlineStr"/>
+      <c r="I112" s="3" t="inlineStr"/>
+      <c r="J112" s="3" t="inlineStr"/>
+      <c r="K112" s="3" t="inlineStr"/>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>(626) 963-1611</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; developmentally appropriate play-based</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr"/>
+      <c r="O112" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P112" s="3" t="inlineStr">
+        <is>
+          <t>https://www.glendorausd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q112" s="4" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>Hawthorne School District</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>0616560</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>13885 Hawthorne Boulevard, Hawthorne, CA 90250</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr"/>
+      <c r="H113" s="7" t="inlineStr"/>
+      <c r="I113" s="7" t="inlineStr"/>
+      <c r="J113" s="7" t="inlineStr"/>
+      <c r="K113" s="7" t="inlineStr"/>
+      <c r="L113" s="7" t="inlineStr">
+        <is>
+          <t>(310) 676-2276</t>
+        </is>
+      </c>
+      <c r="M113" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start</t>
+        </is>
+      </c>
+      <c r="N113" s="7" t="inlineStr"/>
+      <c r="O113" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P113" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hawthorne.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q113" s="8" t="inlineStr">
+        <is>
+          <t>Elementary district. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>Lennox School District</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>0621540</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>8200</v>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>10319 South Firmona Avenue, Lennox, CA 90304</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr"/>
+      <c r="H114" s="3" t="inlineStr"/>
+      <c r="I114" s="3" t="inlineStr"/>
+      <c r="J114" s="3" t="inlineStr"/>
+      <c r="K114" s="3" t="inlineStr"/>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>(310) 695-4000</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>Head Start; CSPP</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr"/>
+      <c r="O114" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P114" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lennox.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q114" s="4" t="inlineStr">
+        <is>
+          <t>Elementary district serving low-income community. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>Temple City Unified</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>0638910</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="n">
+        <v>5300</v>
+      </c>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>9700 Las Tunas Drive, Temple City, CA 91780</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr"/>
+      <c r="H115" s="7" t="inlineStr"/>
+      <c r="I115" s="7" t="inlineStr"/>
+      <c r="J115" s="7" t="inlineStr"/>
+      <c r="K115" s="7" t="inlineStr"/>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>(626) 548-5000</t>
+        </is>
+      </c>
+      <c r="M115" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N115" s="7" t="inlineStr"/>
+      <c r="O115" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P115" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tcusd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q115" s="8" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>Monrovia Unified</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>0625470</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>4900</v>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>325 East Huntington Drive, Monrovia, CA 91016</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>Angel</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>Arias</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>Principal, Canyon Early Learning Center</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="inlineStr"/>
+      <c r="K116" s="3" t="inlineStr"/>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>(626) 471-2001</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; California Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr"/>
+      <c r="O116" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P116" s="3" t="inlineStr">
+        <is>
+          <t>https://www.monroviausd.net/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q116" s="4" t="inlineStr">
+        <is>
+          <t>Angel Arias confirmed as Principal of Canyon Early Learning Center. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>Bonita Unified</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>0605310</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="n">
+        <v>7700</v>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>115 West Allen Avenue, San Dimas, CA 91773</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr"/>
+      <c r="H117" s="7" t="inlineStr"/>
+      <c r="I117" s="7" t="inlineStr"/>
+      <c r="J117" s="7" t="inlineStr"/>
+      <c r="K117" s="7" t="inlineStr"/>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>(909) 971-8200</t>
+        </is>
+      </c>
+      <c r="M117" s="7" t="inlineStr">
+        <is>
+          <t>BLAST Preschool Program — research-based, inclusive model recognized by CalECSE</t>
+        </is>
+      </c>
+      <c r="N117" s="7" t="inlineStr"/>
+      <c r="O117" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+QRIS | BLAST Preschool Program recognized by CalECSE for exemplary inclusive practices | bonita.k12.ca.us | 2024</t>
+        </is>
+      </c>
+      <c r="P117" s="7" t="inlineStr">
+        <is>
+          <t>https://do.bonita.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q117" s="8" t="inlineStr">
+        <is>
+          <t>BLAST program recognition = strong program quality signal. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>Duarte Unified</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>0611790</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>3800</v>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>1620 Huntington Drive, Duarte, CA 91010</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr"/>
+      <c r="H118" s="3" t="inlineStr"/>
+      <c r="I118" s="3" t="inlineStr"/>
+      <c r="J118" s="3" t="inlineStr"/>
+      <c r="K118" s="3" t="inlineStr"/>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>(626) 599-5000</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; play-based curriculum</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr"/>
+      <c r="O118" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P118" s="3" t="inlineStr">
+        <is>
+          <t>https://www.duarte.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q118" s="4" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>Whittier City School District</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>0641880</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="n">
+        <v>8800</v>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>7330 Washington Avenue, Whittier, CA 90602</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr"/>
+      <c r="H119" s="7" t="inlineStr"/>
+      <c r="I119" s="7" t="inlineStr"/>
+      <c r="J119" s="7" t="inlineStr"/>
+      <c r="K119" s="7" t="inlineStr"/>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>(562) 789-3000</t>
+        </is>
+      </c>
+      <c r="M119" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; developmentally appropriate</t>
+        </is>
+      </c>
+      <c r="N119" s="7" t="inlineStr"/>
+      <c r="O119" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P119" s="7" t="inlineStr">
+        <is>
+          <t>https://www.whittiercity.net/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q119" s="8" t="inlineStr">
+        <is>
+          <t>Elementary district. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>Little Lake City School District</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>0621900</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>10515 Pioneer Boulevard, Santa Fe Springs, CA 90670</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr"/>
+      <c r="H120" s="3" t="inlineStr"/>
+      <c r="I120" s="3" t="inlineStr"/>
+      <c r="J120" s="3" t="inlineStr"/>
+      <c r="K120" s="3" t="inlineStr"/>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>(562) 868-8241</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; play-based</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr"/>
+      <c r="O120" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P120" s="3" t="inlineStr">
+        <is>
+          <t>https://www.llcsd.net/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q120" s="4" t="inlineStr">
+        <is>
+          <t>Elementary district. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>Charter Oak Unified</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>0607710</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>20240 East Cienega Avenue, Covina, CA 91724</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr"/>
+      <c r="H121" s="7" t="inlineStr"/>
+      <c r="I121" s="7" t="inlineStr"/>
+      <c r="J121" s="7" t="inlineStr"/>
+      <c r="K121" s="7" t="inlineStr"/>
+      <c r="L121" s="7" t="inlineStr">
+        <is>
+          <t>(626) 966-8331</t>
+        </is>
+      </c>
+      <c r="M121" s="7" t="inlineStr">
+        <is>
+          <t>L.E.A.P. Program (Learn and Explore Academic Preschool)</t>
+        </is>
+      </c>
+      <c r="N121" s="7" t="inlineStr"/>
+      <c r="O121" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Program | L.E.A.P. branded preschool program in operation | cousd.net | 2024</t>
+        </is>
+      </c>
+      <c r="P121" s="7" t="inlineStr">
+        <is>
+          <t>https://www.cousd.net/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q121" s="8" t="inlineStr">
+        <is>
+          <t>L.E.A.P. program. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>South Whittier School District</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>0637470</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>6700</v>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>14114 Anola Street, Whittier, CA 90604</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr"/>
+      <c r="H122" s="3" t="inlineStr"/>
+      <c r="I122" s="3" t="inlineStr"/>
+      <c r="J122" s="3" t="inlineStr"/>
+      <c r="K122" s="3" t="inlineStr"/>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>(562) 944-6231</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr"/>
+      <c r="O122" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P122" s="3" t="inlineStr">
+        <is>
+          <t>https://www.swsd.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q122" s="4" t="inlineStr">
+        <is>
+          <t>Elementary district. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>La Canada Unified</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>0619860</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="n">
+        <v>3900</v>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>4490 Cornishon Avenue, La Canada Flintridge, CA 91011</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr"/>
+      <c r="H123" s="7" t="inlineStr"/>
+      <c r="I123" s="7" t="inlineStr"/>
+      <c r="J123" s="7" t="inlineStr"/>
+      <c r="K123" s="7" t="inlineStr"/>
+      <c r="L123" s="7" t="inlineStr">
+        <is>
+          <t>(818) 952-8300</t>
+        </is>
+      </c>
+      <c r="M123" s="7" t="inlineStr">
+        <is>
+          <t>TK/PreK aligned with CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N123" s="7" t="inlineStr"/>
+      <c r="O123" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P123" s="7" t="inlineStr">
+        <is>
+          <t>https://www.lcusd.net/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q123" s="8" t="inlineStr">
+        <is>
+          <t>Small affluent district. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>Newport-Mesa Unified</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>0627120</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>21800</v>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>2985 Bear Street, Costa Mesa, CA 92626</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>Kathleen</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>Leary</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>Director of Early Learning</t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>kleary@nmusd.us</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>(949) 515-6828</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>CA Preschool Learning Foundations; play-based</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr"/>
+      <c r="O124" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P124" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nmusd.us/departments/educational-services/early-learning</t>
+        </is>
+      </c>
+      <c r="Q124" s="4" t="inlineStr">
+        <is>
+          <t>High-confidence contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>Tustin Unified</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>0639600</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>300 South C Street, Tustin, CA 92780</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr"/>
+      <c r="H125" s="7" t="inlineStr"/>
+      <c r="I125" s="7" t="inlineStr"/>
+      <c r="J125" s="7" t="inlineStr"/>
+      <c r="K125" s="7" t="inlineStr"/>
+      <c r="L125" s="7" t="inlineStr">
+        <is>
+          <t>(714) 730-7301</t>
+        </is>
+      </c>
+      <c r="M125" s="7" t="inlineStr">
+        <is>
+          <t>CA Preschool Learning Foundations; CSPP</t>
+        </is>
+      </c>
+      <c r="N125" s="7" t="inlineStr"/>
+      <c r="O125" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P125" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tustin.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q125" s="8" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>Brea Olinda Unified</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>0605550</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>1 Civic Center Circle, Brea, CA 92821</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>Amy</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>Shultz</t>
+        </is>
+      </c>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>Director of Educational Services (PreK)</t>
+        </is>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>ashultz@bousd.us</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>(714) 990-7581</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>CA Preschool Learning Foundations; play-based</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr"/>
+      <c r="O126" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P126" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bousd.us/departments/educational-services</t>
+        </is>
+      </c>
+      <c r="Q126" s="4" t="inlineStr">
+        <is>
+          <t>High-confidence contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>La Habra City School District</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>0620100</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>500 North Walnut Street, La Habra, CA 90631</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr"/>
+      <c r="H127" s="7" t="inlineStr"/>
+      <c r="I127" s="7" t="inlineStr"/>
+      <c r="J127" s="7" t="inlineStr"/>
+      <c r="K127" s="7" t="inlineStr"/>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>(562) 690-2305</t>
+        </is>
+      </c>
+      <c r="M127" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start</t>
+        </is>
+      </c>
+      <c r="N127" s="7" t="inlineStr"/>
+      <c r="O127" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P127" s="7" t="inlineStr">
+        <is>
+          <t>https://www.lhcsd.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q127" s="8" t="inlineStr">
+        <is>
+          <t>Elementary district. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>Ocean View School District</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>0628260</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>17200 Pinehurst Lane, Huntington Beach, CA 92647</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr"/>
+      <c r="H128" s="3" t="inlineStr"/>
+      <c r="I128" s="3" t="inlineStr"/>
+      <c r="J128" s="3" t="inlineStr"/>
+      <c r="K128" s="3" t="inlineStr"/>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>(714) 847-2551</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr"/>
+      <c r="O128" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P128" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ovsd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q128" s="4" t="inlineStr">
+        <is>
+          <t>Elementary district. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>Westminster School District</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>0641670</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="n">
+        <v>8600</v>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>14121 Cedarwood Avenue, Westminster, CA 92683</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr"/>
+      <c r="H129" s="7" t="inlineStr"/>
+      <c r="I129" s="7" t="inlineStr"/>
+      <c r="J129" s="7" t="inlineStr"/>
+      <c r="K129" s="7" t="inlineStr"/>
+      <c r="L129" s="7" t="inlineStr">
+        <is>
+          <t>(714) 894-7311</t>
+        </is>
+      </c>
+      <c r="M129" s="7" t="inlineStr">
+        <is>
+          <t>CA Preschool Learning Foundations; CSPP</t>
+        </is>
+      </c>
+      <c r="N129" s="7" t="inlineStr"/>
+      <c r="O129" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+QRIS | District ECE sites achieved 5-star QRIS quality rating | wsd.k12.ca.us | 2024</t>
+        </is>
+      </c>
+      <c r="P129" s="7" t="inlineStr">
+        <is>
+          <t>https://www.wsd.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q129" s="8" t="inlineStr">
+        <is>
+          <t>5-star QRIS sites = program quality signal. Elementary district. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>Cypress School District</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>0610500</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>5300</v>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>9470 Moody Street, Cypress, CA 90630</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr"/>
+      <c r="H130" s="3" t="inlineStr"/>
+      <c r="I130" s="3" t="inlineStr"/>
+      <c r="J130" s="3" t="inlineStr"/>
+      <c r="K130" s="3" t="inlineStr"/>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>(714) 220-6900</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>CA Preschool Learning Foundations; CSPP</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr"/>
+      <c r="O130" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+QRIS | ECE programs achieved 5-star QRIS rating | cypsd.org | 2024</t>
+        </is>
+      </c>
+      <c r="P130" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cypsd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q130" s="4" t="inlineStr">
+        <is>
+          <t>5-star QRIS sites. Elementary district. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>Fountain Valley School District</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>0614490</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>10055 Slater Avenue, Fountain Valley, CA 92708</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr"/>
+      <c r="H131" s="7" t="inlineStr"/>
+      <c r="I131" s="7" t="inlineStr"/>
+      <c r="J131" s="7" t="inlineStr"/>
+      <c r="K131" s="7" t="inlineStr"/>
+      <c r="L131" s="7" t="inlineStr">
+        <is>
+          <t>(714) 843-3200</t>
+        </is>
+      </c>
+      <c r="M131" s="7" t="inlineStr">
+        <is>
+          <t>CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N131" s="7" t="inlineStr"/>
+      <c r="O131" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P131" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fvsd.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q131" s="8" t="inlineStr">
+        <is>
+          <t>Elementary district. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>Los Alamitos Unified</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>0622380</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>10293 Bloomfield Street, Los Alamitos, CA 90720</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr"/>
+      <c r="H132" s="3" t="inlineStr"/>
+      <c r="I132" s="3" t="inlineStr"/>
+      <c r="J132" s="3" t="inlineStr"/>
+      <c r="K132" s="3" t="inlineStr"/>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>(562) 799-4700</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>CA Preschool Learning Foundations; TK</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr"/>
+      <c r="O132" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P132" s="3" t="inlineStr">
+        <is>
+          <t>https://www.losal.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q132" s="4" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>Savanna School District</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>0635250</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>1330 South Knott Avenue, Anaheim, CA 92804</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr"/>
+      <c r="H133" s="7" t="inlineStr"/>
+      <c r="I133" s="7" t="inlineStr"/>
+      <c r="J133" s="7" t="inlineStr"/>
+      <c r="K133" s="7" t="inlineStr"/>
+      <c r="L133" s="7" t="inlineStr">
+        <is>
+          <t>(714) 236-3800</t>
+        </is>
+      </c>
+      <c r="M133" s="7" t="inlineStr">
+        <is>
+          <t>BRIGHT Learners Academy program</t>
+        </is>
+      </c>
+      <c r="N133" s="7" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="O133" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Program | BRIGHT Learners Academy launched 2023 — dedicated branded ECE program | savsd.org | 2023</t>
+        </is>
+      </c>
+      <c r="P133" s="7" t="inlineStr">
+        <is>
+          <t>https://www.savsd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q133" s="8" t="inlineStr">
+        <is>
+          <t>BRIGHT Learners Academy launch in 2023 signals active ECE investment. Small elementary district. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>San Marcos Unified</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>0634740</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>23800</v>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>255 Pico Avenue, San Marcos, CA 92069</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>Anileydi</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>Diaz-Chavez</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>Early Childhood Education Coordinator</t>
+        </is>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>anileydi.diaz-chavez@smusd.org</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>(760) 290-2597</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>CA Preschool Learning Foundations; CSPP</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr"/>
+      <c r="O134" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P134" s="3" t="inlineStr">
+        <is>
+          <t>https://www.smusd.org/departments/educational-services/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q134" s="4" t="inlineStr">
+        <is>
+          <t>High-confidence contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>Escondido Union School District</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>0613230</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="n">
+        <v>15500</v>
+      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>2310 Aldergrove Avenue, Escondido, CA 92029</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr"/>
+      <c r="H135" s="7" t="inlineStr"/>
+      <c r="I135" s="7" t="inlineStr"/>
+      <c r="J135" s="7" t="inlineStr"/>
+      <c r="K135" s="7" t="inlineStr"/>
+      <c r="L135" s="7" t="inlineStr">
+        <is>
+          <t>(760) 432-2400</t>
+        </is>
+      </c>
+      <c r="M135" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N135" s="7" t="inlineStr"/>
+      <c r="O135" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P135" s="7" t="inlineStr">
+        <is>
+          <t>https://www.eusd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q135" s="8" t="inlineStr">
+        <is>
+          <t>Elementary district (note: separate from Escondido Union High School District). ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>National School District</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>0626700</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>1500 N Avenue, National City, CA 91950</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr"/>
+      <c r="H136" s="3" t="inlineStr"/>
+      <c r="I136" s="3" t="inlineStr"/>
+      <c r="J136" s="3" t="inlineStr"/>
+      <c r="K136" s="3" t="inlineStr"/>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>(619) 336-7500</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr"/>
+      <c r="O136" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P136" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nsd.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q136" s="4" t="inlineStr">
+        <is>
+          <t>Elementary district. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>Santee School District</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>0635010</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="n">
+        <v>7400</v>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>9625 Cuyamaca Street, Santee, CA 92071</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr"/>
+      <c r="H137" s="7" t="inlineStr"/>
+      <c r="I137" s="7" t="inlineStr"/>
+      <c r="J137" s="7" t="inlineStr"/>
+      <c r="K137" s="7" t="inlineStr"/>
+      <c r="L137" s="7" t="inlineStr">
+        <is>
+          <t>(619) 258-2300</t>
+        </is>
+      </c>
+      <c r="M137" s="7" t="inlineStr">
+        <is>
+          <t>YALE Preschool program</t>
+        </is>
+      </c>
+      <c r="N137" s="7" t="inlineStr"/>
+      <c r="O137" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Program | YALE Preschool program in operation | santeesd.net | 2024</t>
+        </is>
+      </c>
+      <c r="P137" s="7" t="inlineStr">
+        <is>
+          <t>https://www.santeesd.net/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q137" s="8" t="inlineStr">
+        <is>
+          <t>YALE branded program. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>Lemon Grove School District</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>0621390</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>4900</v>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>8025 Lincoln Street, Lemon Grove, CA 91945</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>Melvetta</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>Owens</t>
+        </is>
+      </c>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>Director of Educational Services (Early Childhood)</t>
+        </is>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>melvetta.owens@lemongrovesd.net</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>(619) 825-5637</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr"/>
+      <c r="O138" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Expansion | Broke ground on new ECE center 2024 | lemongrovesd.net | 2024</t>
+        </is>
+      </c>
+      <c r="P138" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lemongrovesd.net/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q138" s="4" t="inlineStr">
+        <is>
+          <t>High-confidence contact. New ECE facility under construction — strong expansion signal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>Spring Valley School District</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>0637590</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>3100 Sweetwater Springs Blvd, Spring Valley, CA 91977</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>Charmaine</t>
+        </is>
+      </c>
+      <c r="H139" s="7" t="inlineStr">
+        <is>
+          <t>Lawson</t>
+        </is>
+      </c>
+      <c r="I139" s="7" t="inlineStr">
+        <is>
+          <t>Director of Early Childhood Education</t>
+        </is>
+      </c>
+      <c r="J139" s="7" t="inlineStr">
+        <is>
+          <t>charmaine.lawson@lmsvschools.org</t>
+        </is>
+      </c>
+      <c r="K139" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t>(619) 771-6082</t>
+        </is>
+      </c>
+      <c r="M139" s="7" t="inlineStr">
+        <is>
+          <t>CA Preschool Learning Foundations; CSPP</t>
+        </is>
+      </c>
+      <c r="N139" s="7" t="inlineStr"/>
+      <c r="O139" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P139" s="7" t="inlineStr">
+        <is>
+          <t>https://www.lmsvschools.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q139" s="8" t="inlineStr">
+        <is>
+          <t>High-confidence contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>Lakeside Union School District</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>0620250</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>4900</v>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>12335 Woodside Avenue, Lakeside, CA 92040</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr"/>
+      <c r="H140" s="3" t="inlineStr"/>
+      <c r="I140" s="3" t="inlineStr"/>
+      <c r="J140" s="3" t="inlineStr"/>
+      <c r="K140" s="3" t="inlineStr"/>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>(619) 390-2600</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr"/>
+      <c r="O140" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P140" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lsusd.net/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q140" s="4" t="inlineStr">
+        <is>
+          <t>Elementary district. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>South Bay Union School District</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>0637380</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="n">
+        <v>7700</v>
+      </c>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>601 Elm Avenue, Imperial Beach, CA 91932</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr"/>
+      <c r="H141" s="7" t="inlineStr"/>
+      <c r="I141" s="7" t="inlineStr"/>
+      <c r="J141" s="7" t="inlineStr"/>
+      <c r="K141" s="7" t="inlineStr"/>
+      <c r="L141" s="7" t="inlineStr">
+        <is>
+          <t>(619) 628-1600</t>
+        </is>
+      </c>
+      <c r="M141" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start</t>
+        </is>
+      </c>
+      <c r="N141" s="7" t="inlineStr"/>
+      <c r="O141" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P141" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sbusd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q141" s="8" t="inlineStr">
+        <is>
+          <t>Elementary district. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>Del Mar Union School District</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>0610920</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>3800</v>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>225 Ninth Street, Del Mar, CA 92014</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr"/>
+      <c r="H142" s="3" t="inlineStr"/>
+      <c r="I142" s="3" t="inlineStr"/>
+      <c r="J142" s="3" t="inlineStr"/>
+      <c r="K142" s="3" t="inlineStr"/>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>(858) 755-9301</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>Reggio Emilia-inspired approach; CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr"/>
+      <c r="O142" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P142" s="3" t="inlineStr">
+        <is>
+          <t>https://www.dmusd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q142" s="4" t="inlineStr">
+        <is>
+          <t>Small affluent district; Reggio-inspired approach. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>Desert Sands Unified</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>0611010</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="n">
+        <v>27500</v>
+      </c>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>47950 Dune Palms Road, La Quinta, CA 92253</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr"/>
+      <c r="H143" s="7" t="inlineStr"/>
+      <c r="I143" s="7" t="inlineStr"/>
+      <c r="J143" s="7" t="inlineStr"/>
+      <c r="K143" s="7" t="inlineStr"/>
+      <c r="L143" s="7" t="inlineStr">
+        <is>
+          <t>(760) 777-4200</t>
+        </is>
+      </c>
+      <c r="M143" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start; CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N143" s="7" t="inlineStr"/>
+      <c r="O143" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P143" s="7" t="inlineStr">
+        <is>
+          <t>https://www.dsusd.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q143" s="8" t="inlineStr">
+        <is>
+          <t>One of the largest unified districts in Coachella Valley. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>Palm Springs Unified</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>0629190</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>20400</v>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>980 East Tahquitz Canyon Way, Palm Springs, CA 92262</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr"/>
+      <c r="H144" s="3" t="inlineStr"/>
+      <c r="I144" s="3" t="inlineStr"/>
+      <c r="J144" s="3" t="inlineStr"/>
+      <c r="K144" s="3" t="inlineStr"/>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>(760) 416-6000</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start; CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr"/>
+      <c r="O144" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P144" s="3" t="inlineStr">
+        <is>
+          <t>https://www.psusd.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q144" s="4" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>Coachella Valley Unified</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>0609120</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="n">
+        <v>21600</v>
+      </c>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>87-225 Church Street, Coachella, CA 92236</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr"/>
+      <c r="H145" s="7" t="inlineStr"/>
+      <c r="I145" s="7" t="inlineStr">
+        <is>
+          <t>Director of Early Learners (position open as of 2025)</t>
+        </is>
+      </c>
+      <c r="J145" s="7" t="inlineStr"/>
+      <c r="K145" s="7" t="inlineStr"/>
+      <c r="L145" s="7" t="inlineStr">
+        <is>
+          <t>(760) 848-1000</t>
+        </is>
+      </c>
+      <c r="M145" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start; Migrant Education PreK</t>
+        </is>
+      </c>
+      <c r="N145" s="7" t="inlineStr"/>
+      <c r="O145" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Leadership | Director of Early Learners position open as of 2025 — new hire signal | cvusd.us | 2025</t>
+        </is>
+      </c>
+      <c r="P145" s="7" t="inlineStr">
+        <is>
+          <t>https://www.cvusd.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q145" s="8" t="inlineStr">
+        <is>
+          <t>Director of Early Learners position open — leadership transition = open window. Large migrant education population.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>Jurupa Unified</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>0619230</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>19800</v>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>4850 Pedley Road, Jurupa Valley, CA 92509</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>Katrina</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>Brooks</t>
+        </is>
+      </c>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>Early Childhood Education Coordinator</t>
+        </is>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>katrina_brooks@jusd.k12.ca.us</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>(951) 360-4100</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>CA Preschool Learning Foundations; CSPP</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr"/>
+      <c r="O146" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+QRIS | District ECE sites achieved 5-star QRIS quality rating | jusd.k12.ca.us | 2024</t>
+        </is>
+      </c>
+      <c r="P146" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jusd.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q146" s="4" t="inlineStr">
+        <is>
+          <t>High-confidence contact. 5-star QRIS rating signals strong program investment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>Lake Elsinore Unified</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>0620190</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="n">
+        <v>20700</v>
+      </c>
+      <c r="F147" s="7" t="inlineStr">
+        <is>
+          <t>545 Chaney Street, Lake Elsinore, CA 92530</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="inlineStr"/>
+      <c r="H147" s="7" t="inlineStr"/>
+      <c r="I147" s="7" t="inlineStr"/>
+      <c r="J147" s="7" t="inlineStr"/>
+      <c r="K147" s="7" t="inlineStr"/>
+      <c r="L147" s="7" t="inlineStr">
+        <is>
+          <t>(951) 253-7000</t>
+        </is>
+      </c>
+      <c r="M147" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start</t>
+        </is>
+      </c>
+      <c r="N147" s="7" t="inlineStr"/>
+      <c r="O147" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P147" s="7" t="inlineStr">
+        <is>
+          <t>https://www.leusd.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q147" s="8" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>Perris Elementary School District</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>0630000</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>11700</v>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>143 East First Street, Perris, CA 92570</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr"/>
+      <c r="H148" s="3" t="inlineStr"/>
+      <c r="I148" s="3" t="inlineStr"/>
+      <c r="J148" s="3" t="inlineStr"/>
+      <c r="K148" s="3" t="inlineStr"/>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>(951) 657-3118</t>
+        </is>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr"/>
+      <c r="O148" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P148" s="3" t="inlineStr">
+        <is>
+          <t>https://www.perris.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q148" s="4" t="inlineStr">
+        <is>
+          <t>Elementary district. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>San Jacinto Unified</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>0634560</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="n">
+        <v>9900</v>
+      </c>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>2045 South San Jacinto Avenue, San Jacinto, CA 92583</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="inlineStr"/>
+      <c r="H149" s="7" t="inlineStr"/>
+      <c r="I149" s="7" t="inlineStr"/>
+      <c r="J149" s="7" t="inlineStr"/>
+      <c r="K149" s="7" t="inlineStr"/>
+      <c r="L149" s="7" t="inlineStr">
+        <is>
+          <t>(951) 654-7427</t>
+        </is>
+      </c>
+      <c r="M149" s="7" t="inlineStr">
+        <is>
+          <t>CA Preschool Learning Foundations; CSPP</t>
+        </is>
+      </c>
+      <c r="N149" s="7" t="inlineStr"/>
+      <c r="O149" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+QRIS | District ECE sites achieved 5-star QRIS quality rating | sanjacintousd.org | 2024</t>
+        </is>
+      </c>
+      <c r="P149" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sanjacintousd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q149" s="8" t="inlineStr">
+        <is>
+          <t>5-star QRIS rating. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>Val Verde Unified</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>0640290</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>12800</v>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>975 West Morgan Street, Perris, CA 92571</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr"/>
+      <c r="H150" s="3" t="inlineStr"/>
+      <c r="I150" s="3" t="inlineStr"/>
+      <c r="J150" s="3" t="inlineStr"/>
+      <c r="K150" s="3" t="inlineStr"/>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>(951) 940-6100</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr"/>
+      <c r="O150" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P150" s="3" t="inlineStr">
+        <is>
+          <t>https://www.valverdeschools.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q150" s="4" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>Yucaipa-Calimesa Joint Unified</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t>0641970</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>San Bernardino</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="n">
+        <v>10200</v>
+      </c>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>12797 Third Street, Yucaipa, CA 92399</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr"/>
+      <c r="H151" s="7" t="inlineStr"/>
+      <c r="I151" s="7" t="inlineStr"/>
+      <c r="J151" s="7" t="inlineStr"/>
+      <c r="K151" s="7" t="inlineStr"/>
+      <c r="L151" s="7" t="inlineStr">
+        <is>
+          <t>(909) 797-0174</t>
+        </is>
+      </c>
+      <c r="M151" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N151" s="7" t="inlineStr"/>
+      <c r="O151" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Expansion | Early Childhood Education Center serves as hub for district ECE programs | ycjusd.us | 2024</t>
+        </is>
+      </c>
+      <c r="P151" s="7" t="inlineStr">
+        <is>
+          <t>https://www.ycjusd.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q151" s="8" t="inlineStr">
+        <is>
+          <t>Dedicated ECE Center. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>Ontario-Montclair School District</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>0628710</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>San Bernardino</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>24500</v>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>950 West D Street, Ontario, CA 91762</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr"/>
+      <c r="H152" s="3" t="inlineStr"/>
+      <c r="I152" s="3" t="inlineStr"/>
+      <c r="J152" s="3" t="inlineStr"/>
+      <c r="K152" s="3" t="inlineStr"/>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>(909) 459-2500</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start; CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr"/>
+      <c r="O152" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P152" s="3" t="inlineStr">
+        <is>
+          <t>https://www.omsd.net/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q152" s="4" t="inlineStr">
+        <is>
+          <t>Large elementary district. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>Colton Joint Unified</t>
+        </is>
+      </c>
+      <c r="B153" s="7" t="inlineStr">
+        <is>
+          <t>0609030</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>San Bernardino</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="n">
+        <v>23500</v>
+      </c>
+      <c r="F153" s="7" t="inlineStr">
+        <is>
+          <t>1212 Valencia Drive, Colton, CA 92324</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr"/>
+      <c r="H153" s="7" t="inlineStr"/>
+      <c r="I153" s="7" t="inlineStr"/>
+      <c r="J153" s="7" t="inlineStr"/>
+      <c r="K153" s="7" t="inlineStr"/>
+      <c r="L153" s="7" t="inlineStr">
+        <is>
+          <t>(909) 580-5000</t>
+        </is>
+      </c>
+      <c r="M153" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start</t>
+        </is>
+      </c>
+      <c r="N153" s="7" t="inlineStr"/>
+      <c r="O153" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P153" s="7" t="inlineStr">
+        <is>
+          <t>https://www.cjusd.net/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q153" s="8" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>Upland Unified</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>0639900</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>San Bernardino</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>9800</v>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>390 North Euclid Avenue, Upland, CA 91786</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>Mathew</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>Kodama</t>
+        </is>
+      </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>Early Childhood Education Coordinator</t>
+        </is>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>mathew_kodama@upland.k12.ca.us</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>(909) 985-1864</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>Step Up Preschool program; CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr"/>
+      <c r="O154" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Program | Step Up Preschool dedicated branded ECE program | upland.k12.ca.us | 2024</t>
+        </is>
+      </c>
+      <c r="P154" s="3" t="inlineStr">
+        <is>
+          <t>https://www.upland.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q154" s="4" t="inlineStr">
+        <is>
+          <t>High-confidence contact. Step Up Preschool branded program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>Hesperia Unified</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>0617070</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="inlineStr">
+        <is>
+          <t>San Bernardino</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="n">
+        <v>21700</v>
+      </c>
+      <c r="F155" s="7" t="inlineStr">
+        <is>
+          <t>15576 Main Street, Hesperia, CA 92345</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr"/>
+      <c r="H155" s="7" t="inlineStr"/>
+      <c r="I155" s="7" t="inlineStr"/>
+      <c r="J155" s="7" t="inlineStr"/>
+      <c r="K155" s="7" t="inlineStr"/>
+      <c r="L155" s="7" t="inlineStr">
+        <is>
+          <t>(760) 244-4411</t>
+        </is>
+      </c>
+      <c r="M155" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start</t>
+        </is>
+      </c>
+      <c r="N155" s="7" t="inlineStr"/>
+      <c r="O155" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P155" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hesperiausd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q155" s="8" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>Apple Valley Unified</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>0602310</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>San Bernardino</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>14600</v>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>12555 Navajo Road, Apple Valley, CA 92308</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr"/>
+      <c r="H156" s="3" t="inlineStr"/>
+      <c r="I156" s="3" t="inlineStr"/>
+      <c r="J156" s="3" t="inlineStr"/>
+      <c r="K156" s="3" t="inlineStr"/>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>(760) 247-8001</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr"/>
+      <c r="O156" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P156" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avusd.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q156" s="4" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t>Victor Elementary School District</t>
+        </is>
+      </c>
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t>0640530</t>
+        </is>
+      </c>
+      <c r="C157" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D157" s="7" t="inlineStr">
+        <is>
+          <t>San Bernardino</t>
+        </is>
+      </c>
+      <c r="E157" s="7" t="n">
+        <v>7900</v>
+      </c>
+      <c r="F157" s="7" t="inlineStr">
+        <is>
+          <t>15579 8th Street, Victorville, CA 92395</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="inlineStr"/>
+      <c r="H157" s="7" t="inlineStr"/>
+      <c r="I157" s="7" t="inlineStr"/>
+      <c r="J157" s="7" t="inlineStr"/>
+      <c r="K157" s="7" t="inlineStr"/>
+      <c r="L157" s="7" t="inlineStr">
+        <is>
+          <t>(760) 245-1691</t>
+        </is>
+      </c>
+      <c r="M157" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N157" s="7" t="inlineStr"/>
+      <c r="O157" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P157" s="7" t="inlineStr">
+        <is>
+          <t>https://www.vesd.net/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q157" s="8" t="inlineStr">
+        <is>
+          <t>Elementary district. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>Etiwanda School District</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>0613560</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>San Bernardino</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>12700</v>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>6061 East Avenue, Rancho Cucamonga, CA 91739</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr"/>
+      <c r="H158" s="3" t="inlineStr"/>
+      <c r="I158" s="3" t="inlineStr"/>
+      <c r="J158" s="3" t="inlineStr"/>
+      <c r="K158" s="3" t="inlineStr"/>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>(909) 899-2451</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>CA Preschool Learning Foundations; TK</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr"/>
+      <c r="O158" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P158" s="3" t="inlineStr">
+        <is>
+          <t>https://www.etiwanda.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q158" s="4" t="inlineStr">
+        <is>
+          <t>Elementary district. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t>Barstow Unified</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>0603840</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>San Bernardino</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="n">
+        <v>5900</v>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>551 South Avenue H, Barstow, CA 92311</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr"/>
+      <c r="H159" s="7" t="inlineStr"/>
+      <c r="I159" s="7" t="inlineStr"/>
+      <c r="J159" s="7" t="inlineStr"/>
+      <c r="K159" s="7" t="inlineStr"/>
+      <c r="L159" s="7" t="inlineStr">
+        <is>
+          <t>(760) 255-6000</t>
+        </is>
+      </c>
+      <c r="M159" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start</t>
+        </is>
+      </c>
+      <c r="N159" s="7" t="inlineStr"/>
+      <c r="O159" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P159" s="7" t="inlineStr">
+        <is>
+          <t>https://www.barstow.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q159" s="8" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>Panama-Buena Vista Union School District</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>0629220</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>Kern</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>14800</v>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>4200 Ashe Road, Bakersfield, CA 93313</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr"/>
+      <c r="H160" s="3" t="inlineStr"/>
+      <c r="I160" s="3" t="inlineStr"/>
+      <c r="J160" s="3" t="inlineStr"/>
+      <c r="K160" s="3" t="inlineStr"/>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>(661) 831-8331</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start; CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr"/>
+      <c r="O160" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P160" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pbvusd.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q160" s="4" t="inlineStr">
+        <is>
+          <t>Large elementary district in Bakersfield. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="7" t="inlineStr">
+        <is>
+          <t>Eastside Union School District</t>
+        </is>
+      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>0612420</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>Kern</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="n">
+        <v>9800</v>
+      </c>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>2629 East Avenue I, Lancaster, CA 93535</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="inlineStr"/>
+      <c r="H161" s="7" t="inlineStr"/>
+      <c r="I161" s="7" t="inlineStr"/>
+      <c r="J161" s="7" t="inlineStr"/>
+      <c r="K161" s="7" t="inlineStr"/>
+      <c r="L161" s="7" t="inlineStr">
+        <is>
+          <t>(661) 952-1200</t>
+        </is>
+      </c>
+      <c r="M161" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start</t>
+        </is>
+      </c>
+      <c r="N161" s="7" t="inlineStr"/>
+      <c r="O161" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P161" s="7" t="inlineStr">
+        <is>
+          <t>https://www.eusd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q161" s="8" t="inlineStr">
+        <is>
+          <t>Elementary district (Lancaster). ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>Greenfield Union School District</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>0615780</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>Kern</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>11800</v>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>1624 Fairview Road, Bakersfield, CA 93307</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr"/>
+      <c r="H162" s="3" t="inlineStr"/>
+      <c r="I162" s="3" t="inlineStr"/>
+      <c r="J162" s="3" t="inlineStr"/>
+      <c r="K162" s="3" t="inlineStr"/>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>(661) 837-6000</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start; comprehensive early education programs</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr"/>
+      <c r="O162" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Program | Comprehensive early education programs with multiple sites | greenfieldusd.com | 2024</t>
+        </is>
+      </c>
+      <c r="P162" s="3" t="inlineStr">
+        <is>
+          <t>https://www.greenfieldusd.com/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q162" s="4" t="inlineStr">
+        <is>
+          <t>Large elementary district in South Bakersfield. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="7" t="inlineStr">
+        <is>
+          <t>Delano Union Elementary School District</t>
+        </is>
+      </c>
+      <c r="B163" s="7" t="inlineStr">
+        <is>
+          <t>0610980</t>
+        </is>
+      </c>
+      <c r="C163" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="inlineStr">
+        <is>
+          <t>Kern</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>1405 12th Avenue, Delano, CA 93215</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="inlineStr"/>
+      <c r="H163" s="7" t="inlineStr"/>
+      <c r="I163" s="7" t="inlineStr"/>
+      <c r="J163" s="7" t="inlineStr"/>
+      <c r="K163" s="7" t="inlineStr"/>
+      <c r="L163" s="7" t="inlineStr">
+        <is>
+          <t>(661) 720-4000</t>
+        </is>
+      </c>
+      <c r="M163" s="7" t="inlineStr">
+        <is>
+          <t>First 5 funded SRI Preschool; CSPP</t>
+        </is>
+      </c>
+      <c r="N163" s="7" t="inlineStr"/>
+      <c r="O163" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Grant | First 5 Kern funded SRI Preschool in operation | delano.k12.ca.us | 2024</t>
+        </is>
+      </c>
+      <c r="P163" s="7" t="inlineStr">
+        <is>
+          <t>https://www.delano.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q163" s="8" t="inlineStr">
+        <is>
+          <t>First 5 grant funding = active ECE investment. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>Tehachapi Unified</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>0638820</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>Kern</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>300 South Robinson Street, Tehachapi, CA 93561</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr"/>
+      <c r="H164" s="3" t="inlineStr"/>
+      <c r="I164" s="3" t="inlineStr"/>
+      <c r="J164" s="3" t="inlineStr"/>
+      <c r="K164" s="3" t="inlineStr"/>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>(661) 822-2100</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr"/>
+      <c r="O164" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P164" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tusd.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q164" s="4" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="7" t="inlineStr">
+        <is>
+          <t>Kings Canyon Unified</t>
+        </is>
+      </c>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>0619770</t>
+        </is>
+      </c>
+      <c r="C165" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D165" s="7" t="inlineStr">
+        <is>
+          <t>Fresno</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="n">
+        <v>9900</v>
+      </c>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>675 West Manning Avenue, Reedley, CA 93654</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="inlineStr"/>
+      <c r="H165" s="7" t="inlineStr"/>
+      <c r="I165" s="7" t="inlineStr"/>
+      <c r="J165" s="7" t="inlineStr"/>
+      <c r="K165" s="7" t="inlineStr"/>
+      <c r="L165" s="7" t="inlineStr">
+        <is>
+          <t>(559) 305-7010</t>
+        </is>
+      </c>
+      <c r="M165" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start</t>
+        </is>
+      </c>
+      <c r="N165" s="7" t="inlineStr"/>
+      <c r="O165" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P165" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kcusd.com/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q165" s="8" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>Sanger Unified</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>0634620</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Fresno</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>12200</v>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>1905 Seventh Street, Sanger, CA 93657</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr"/>
+      <c r="H166" s="3" t="inlineStr"/>
+      <c r="I166" s="3" t="inlineStr"/>
+      <c r="J166" s="3" t="inlineStr"/>
+      <c r="K166" s="3" t="inlineStr"/>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>(559) 524-6500</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start; CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr"/>
+      <c r="O166" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P166" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sangerusd.net/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q166" s="4" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="7" t="inlineStr">
+        <is>
+          <t>Selma Unified</t>
+        </is>
+      </c>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>0635610</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>Fresno</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>3036 Thompson Avenue, Selma, CA 93662</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="inlineStr"/>
+      <c r="H167" s="7" t="inlineStr"/>
+      <c r="I167" s="7" t="inlineStr"/>
+      <c r="J167" s="7" t="inlineStr"/>
+      <c r="K167" s="7" t="inlineStr"/>
+      <c r="L167" s="7" t="inlineStr">
+        <is>
+          <t>(559) 898-6500</t>
+        </is>
+      </c>
+      <c r="M167" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N167" s="7" t="inlineStr"/>
+      <c r="O167" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P167" s="7" t="inlineStr">
+        <is>
+          <t>https://www.selmaunified.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q167" s="8" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>Madera Unified</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>0622740</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>Madera</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>9800</v>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>1902 Howard Road, Madera, CA 93637</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr"/>
+      <c r="H168" s="3" t="inlineStr"/>
+      <c r="I168" s="3" t="inlineStr"/>
+      <c r="J168" s="3" t="inlineStr"/>
+      <c r="K168" s="3" t="inlineStr"/>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>(559) 675-4500</t>
+        </is>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>State Preschool (520 students enrolled)</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr"/>
+      <c r="O168" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Program | State Preschool program with 520 enrolled students | maderausd.org | 2024</t>
+        </is>
+      </c>
+      <c r="P168" s="3" t="inlineStr">
+        <is>
+          <t>https://www.maderausd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q168" s="4" t="inlineStr">
+        <is>
+          <t>520-student preschool program. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="7" t="inlineStr">
+        <is>
+          <t>Porterville Unified</t>
+        </is>
+      </c>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>0630870</t>
+        </is>
+      </c>
+      <c r="C169" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>Tulare</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="n">
+        <v>11800</v>
+      </c>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>600 West Grand Avenue, Porterville, CA 93257</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="inlineStr"/>
+      <c r="H169" s="7" t="inlineStr"/>
+      <c r="I169" s="7" t="inlineStr">
+        <is>
+          <t>Director of Early Education (position exists)</t>
+        </is>
+      </c>
+      <c r="J169" s="7" t="inlineStr"/>
+      <c r="K169" s="7" t="inlineStr"/>
+      <c r="L169" s="7" t="inlineStr">
+        <is>
+          <t>(559) 793-2400</t>
+        </is>
+      </c>
+      <c r="M169" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start</t>
+        </is>
+      </c>
+      <c r="N169" s="7" t="inlineStr"/>
+      <c r="O169" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Staffing | Dedicated Director of Early Education role in organizational chart | portervilleusd.org | 2024</t>
+        </is>
+      </c>
+      <c r="P169" s="7" t="inlineStr">
+        <is>
+          <t>https://www.portervilleusd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q169" s="8" t="inlineStr">
+        <is>
+          <t>Director of Early Education position confirmed in org chart — specific name not identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>Tulare City School District</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>0639480</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>Tulare</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>6900</v>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>600 North Cherry Street, Tulare, CA 93274</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr"/>
+      <c r="H170" s="3" t="inlineStr"/>
+      <c r="I170" s="3" t="inlineStr"/>
+      <c r="J170" s="3" t="inlineStr"/>
+      <c r="K170" s="3" t="inlineStr"/>
+      <c r="L170" s="3" t="inlineStr">
+        <is>
+          <t>(559) 685-7200</t>
+        </is>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr"/>
+      <c r="O170" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P170" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tulare.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q170" s="4" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t>Dinuba Unified</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>0611340</t>
+        </is>
+      </c>
+      <c r="C171" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>Tulare</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="n">
+        <v>5400</v>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>1327 East El Monte Way, Dinuba, CA 93618</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr"/>
+      <c r="H171" s="7" t="inlineStr"/>
+      <c r="I171" s="7" t="inlineStr"/>
+      <c r="J171" s="7" t="inlineStr"/>
+      <c r="K171" s="7" t="inlineStr"/>
+      <c r="L171" s="7" t="inlineStr">
+        <is>
+          <t>(559) 595-7200</t>
+        </is>
+      </c>
+      <c r="M171" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; extended day TK programs</t>
+        </is>
+      </c>
+      <c r="N171" s="7" t="inlineStr"/>
+      <c r="O171" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Program | Extended day TK programs in operation | dinuba.k12.ca.us | 2024</t>
+        </is>
+      </c>
+      <c r="P171" s="7" t="inlineStr">
+        <is>
+          <t>https://www.dinuba.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q171" s="8" t="inlineStr">
+        <is>
+          <t>Extended day TK programs. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>Merced City School District</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>0624380</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>Merced</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>11700</v>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>444 West 23rd Street, Merced, CA 95340</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr"/>
+      <c r="H172" s="3" t="inlineStr"/>
+      <c r="I172" s="3" t="inlineStr"/>
+      <c r="J172" s="3" t="inlineStr"/>
+      <c r="K172" s="3" t="inlineStr"/>
+      <c r="L172" s="3" t="inlineStr">
+        <is>
+          <t>(209) 385-6600</t>
+        </is>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start; CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr"/>
+      <c r="O172" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P172" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mcsd.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q172" s="4" t="inlineStr">
+        <is>
+          <t>Elementary district. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="7" t="inlineStr">
+        <is>
+          <t>Atwater Elementary School District</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>0603120</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>Merced</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="n">
+        <v>5900</v>
+      </c>
+      <c r="F173" s="7" t="inlineStr">
+        <is>
+          <t>1401 Broadway Avenue, Atwater, CA 95301</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="inlineStr"/>
+      <c r="H173" s="7" t="inlineStr"/>
+      <c r="I173" s="7" t="inlineStr"/>
+      <c r="J173" s="7" t="inlineStr"/>
+      <c r="K173" s="7" t="inlineStr"/>
+      <c r="L173" s="7" t="inlineStr">
+        <is>
+          <t>(209) 357-6100</t>
+        </is>
+      </c>
+      <c r="M173" s="7" t="inlineStr">
+        <is>
+          <t>CSPP; CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N173" s="7" t="inlineStr"/>
+      <c r="O173" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P173" s="7" t="inlineStr">
+        <is>
+          <t>https://www.atwaterschools.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q173" s="8" t="inlineStr">
+        <is>
+          <t>Elementary district. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>Ceres Unified</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>0607560</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>Stanislaus</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>12800</v>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>2503 Lawrence Street, Ceres, CA 95307</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr"/>
+      <c r="H174" s="3" t="inlineStr"/>
+      <c r="I174" s="3" t="inlineStr"/>
+      <c r="J174" s="3" t="inlineStr"/>
+      <c r="K174" s="3" t="inlineStr"/>
+      <c r="L174" s="3" t="inlineStr">
+        <is>
+          <t>(209) 556-1500</t>
+        </is>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; Head Start</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr"/>
+      <c r="O174" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P174" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ceres.k12.ca.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q174" s="4" t="inlineStr">
+        <is>
+          <t>ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="7" t="inlineStr">
+        <is>
+          <t>Patterson Joint Unified</t>
+        </is>
+      </c>
+      <c r="B175" s="7" t="inlineStr">
+        <is>
+          <t>0629640</t>
+        </is>
+      </c>
+      <c r="C175" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D175" s="7" t="inlineStr">
+        <is>
+          <t>Stanislaus</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F175" s="7" t="inlineStr">
+        <is>
+          <t>510 Keystone Boulevard, Patterson, CA 95363</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="inlineStr"/>
+      <c r="H175" s="7" t="inlineStr"/>
+      <c r="I175" s="7" t="inlineStr"/>
+      <c r="J175" s="7" t="inlineStr"/>
+      <c r="K175" s="7" t="inlineStr"/>
+      <c r="L175" s="7" t="inlineStr">
+        <is>
+          <t>(209) 895-7700</t>
+        </is>
+      </c>
+      <c r="M175" s="7" t="inlineStr">
+        <is>
+          <t>West Valley PreK/TK dedicated school program</t>
+        </is>
+      </c>
+      <c r="N175" s="7" t="inlineStr"/>
+      <c r="O175" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Program | Dedicated West Valley PreK/TK school serves all district preschoolers | pjusd.org | 2024</t>
+        </is>
+      </c>
+      <c r="P175" s="7" t="inlineStr">
+        <is>
+          <t>https://www.pjusd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q175" s="8" t="inlineStr">
+        <is>
+          <t>Dedicated PreK/TK school — strong program investment signal. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>Hanford Elementary School District</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>0616290</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>Kings</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>714 North Douty Street, Hanford, CA 93230</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="inlineStr"/>
+      <c r="H176" s="3" t="inlineStr"/>
+      <c r="I176" s="3" t="inlineStr"/>
+      <c r="J176" s="3" t="inlineStr"/>
+      <c r="K176" s="3" t="inlineStr"/>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>(559) 585-3600</t>
+        </is>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>CSPP; CA Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr"/>
+      <c r="O176" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P176" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hesd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q176" s="4" t="inlineStr">
+        <is>
+          <t>Elementary district. ECE director not publicly identified. Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="7" t="inlineStr">
+        <is>
+          <t>Antioch Unified School District</t>
+        </is>
+      </c>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>0602850</t>
+        </is>
+      </c>
+      <c r="C177" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>Contra Costa</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>510 G Street, Antioch, CA 94509</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr"/>
+      <c r="H177" s="7" t="inlineStr"/>
+      <c r="I177" s="7" t="inlineStr"/>
+      <c r="J177" s="7" t="inlineStr"/>
+      <c r="K177" s="7" t="inlineStr"/>
+      <c r="L177" s="7" t="inlineStr">
+        <is>
+          <t>925-779-7500</t>
+        </is>
+      </c>
+      <c r="M177" s="7" t="inlineStr"/>
+      <c r="N177" s="7" t="inlineStr"/>
+      <c r="O177" s="8" t="inlineStr">
+        <is>
+          <t>Universal Transitional Kindergarten (UTK) implementation required by California; State Preschool programs at multiple elementary sites | https://www.antiochschools.net/ | 2025</t>
+        </is>
+      </c>
+      <c r="P177" s="7" t="inlineStr">
+        <is>
+          <t>https://www.antiochschools.net/staff</t>
+        </is>
+      </c>
+      <c r="Q177" s="8" t="inlineStr">
+        <is>
+          <t>District has Curriculum, Instruction, and Assessment department; staff directory searchable but specific ECE director not listed on public pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>San Leandro Unified School District</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>0634680</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>Alameda</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>835 East 14th Street Suite 200, San Leandro, CA 94577</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="inlineStr"/>
+      <c r="H178" s="3" t="inlineStr"/>
+      <c r="I178" s="3" t="inlineStr"/>
+      <c r="J178" s="3" t="inlineStr"/>
+      <c r="K178" s="3" t="inlineStr"/>
+      <c r="L178" s="3" t="inlineStr">
+        <is>
+          <t>510-667-3500</t>
+        </is>
+      </c>
+      <c r="M178" s="3" t="inlineStr"/>
+      <c r="N178" s="3" t="inlineStr"/>
+      <c r="O178" s="4" t="inlineStr">
+        <is>
+          <t>Early Start 0-3 program; Early Childhood Special Education (ages 3-5) | https://www.slusd.us/ | 2025</t>
+        </is>
+      </c>
+      <c r="P178" s="3" t="inlineStr">
+        <is>
+          <t>https://www.slusd.us/slusd/district-divisions-departments/educational-services-division/</t>
+        </is>
+      </c>
+      <c r="Q178" s="4" t="inlineStr">
+        <is>
+          <t>Educational Services Division oversees curriculum; ECE contact information not publicly listed</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t>Castro Valley Unified School District</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>0611500</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>Alameda</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>4400 Alma Avenue, Castro Valley, CA 94546</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr"/>
+      <c r="H179" s="7" t="inlineStr"/>
+      <c r="I179" s="7" t="inlineStr"/>
+      <c r="J179" s="7" t="inlineStr"/>
+      <c r="K179" s="7" t="inlineStr"/>
+      <c r="L179" s="7" t="inlineStr">
+        <is>
+          <t>510-537-3000</t>
+        </is>
+      </c>
+      <c r="M179" s="7" t="inlineStr"/>
+      <c r="N179" s="7" t="inlineStr"/>
+      <c r="O179" s="8" t="inlineStr">
+        <is>
+          <t>Early Start 0-3 program; Dr. Nia Rashidchi (Superintendent) previously served as Director of Educational Services | https://www.cv.k12.ca.us/ | 2025</t>
+        </is>
+      </c>
+      <c r="P179" s="7" t="inlineStr">
+        <is>
+          <t>https://www.cv.k12.ca.us/educational-services</t>
+        </is>
+      </c>
+      <c r="Q179" s="8" t="inlineStr">
+        <is>
+          <t>Former ECE director (Rashidchi) now Superintendent; specific current ECE director not identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>Dublin Unified School District</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>0600019</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>Alameda</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>13000</v>
+      </c>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>7471 Larkdale Avenue, Dublin, CA 94568</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="inlineStr">
+        <is>
+          <t>Lorianne</t>
+        </is>
+      </c>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>Ventura</t>
+        </is>
+      </c>
+      <c r="I180" s="3" t="inlineStr">
+        <is>
+          <t>Director of Curriculum and Instruction</t>
+        </is>
+      </c>
+      <c r="J180" s="3" t="inlineStr"/>
+      <c r="K180" s="3" t="inlineStr"/>
+      <c r="L180" s="3" t="inlineStr">
+        <is>
+          <t>925-829-6530</t>
+        </is>
+      </c>
+      <c r="M180" s="3" t="inlineStr"/>
+      <c r="N180" s="3" t="inlineStr"/>
+      <c r="O180" s="4" t="inlineStr">
+        <is>
+          <t>Director of Curriculum and Instruction position created; Early Start 0-3 program | https://www.dublin.k12.ca.us/ | 2025</t>
+        </is>
+      </c>
+      <c r="P180" s="3" t="inlineStr">
+        <is>
+          <t>https://www.dublin.k12.ca.us/m/pages/index.jsp?uREC_ID=443957&amp;type=d</t>
+        </is>
+      </c>
+      <c r="Q180" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Lorianne Ventura recently hired as Director of Curriculum &amp; Instruction (start date July 1, 2025); preschool and child care programs available</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="7" t="inlineStr">
+        <is>
+          <t>Pleasanton Unified School District</t>
+        </is>
+      </c>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>0751010</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>Alameda</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>4665 Bernal Avenue, Pleasanton, CA 94566</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="H181" s="7" t="inlineStr">
+        <is>
+          <t>Schrag</t>
+        </is>
+      </c>
+      <c r="I181" s="7" t="inlineStr">
+        <is>
+          <t>Director of Elementary Education</t>
+        </is>
+      </c>
+      <c r="J181" s="7" t="inlineStr"/>
+      <c r="K181" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L181" s="7" t="inlineStr">
+        <is>
+          <t>925-462-4500</t>
+        </is>
+      </c>
+      <c r="M181" s="7" t="inlineStr"/>
+      <c r="N181" s="7" t="inlineStr"/>
+      <c r="O181" s="8" t="inlineStr">
+        <is>
+          <t>PreK-5 program oversight; Coordinator III position for Early Literacy and Numeracy | https://www.pleasantonusd.net/ | 2025</t>
+        </is>
+      </c>
+      <c r="P181" s="7" t="inlineStr">
+        <is>
+          <t>https://www.pleasantonusd.net/departments/educational-services/curriculum-instruction/staff</t>
+        </is>
+      </c>
+      <c r="Q181" s="8" t="inlineStr">
+        <is>
+          <t>David Schrag oversees Elementary/PreK education; email pattern likely d.schrag@pleasantonusd.net or similar; Shay Galletti serves as Coordinator of Early Literacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>San Lorenzo Unified School District</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>0619810</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>Alameda</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>510 Green Street, San Leandro, CA 94577</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="inlineStr"/>
+      <c r="H182" s="3" t="inlineStr"/>
+      <c r="I182" s="3" t="inlineStr"/>
+      <c r="J182" s="3" t="inlineStr"/>
+      <c r="K182" s="3" t="inlineStr"/>
+      <c r="L182" s="3" t="inlineStr">
+        <is>
+          <t>510-278-3700</t>
+        </is>
+      </c>
+      <c r="M182" s="3" t="inlineStr"/>
+      <c r="N182" s="3" t="inlineStr"/>
+      <c r="O182" s="4" t="inlineStr">
+        <is>
+          <t>Pre-K and early childhood services offered | https://www.sanlorenzousd.net/ | 2025</t>
+        </is>
+      </c>
+      <c r="P182" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sanlorenzousd.net/</t>
+        </is>
+      </c>
+      <c r="Q182" s="4" t="inlineStr">
+        <is>
+          <t>ECE contact information not identified during research; recommend direct outreach to district office</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="7" t="inlineStr">
+        <is>
+          <t>Tracy Unified School District</t>
+        </is>
+      </c>
+      <c r="B183" s="7" t="inlineStr">
+        <is>
+          <t>0716430</t>
+        </is>
+      </c>
+      <c r="C183" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D183" s="7" t="inlineStr">
+        <is>
+          <t>San Joaquin</t>
+        </is>
+      </c>
+      <c r="E183" s="7" t="n">
+        <v>16000</v>
+      </c>
+      <c r="F183" s="7" t="inlineStr">
+        <is>
+          <t>3975 Inspection Drive, Tracy, CA 95304</t>
+        </is>
+      </c>
+      <c r="G183" s="7" t="inlineStr"/>
+      <c r="H183" s="7" t="inlineStr"/>
+      <c r="I183" s="7" t="inlineStr"/>
+      <c r="J183" s="7" t="inlineStr"/>
+      <c r="K183" s="7" t="inlineStr"/>
+      <c r="L183" s="7" t="inlineStr">
+        <is>
+          <t>209-831-6800</t>
+        </is>
+      </c>
+      <c r="M183" s="7" t="inlineStr">
+        <is>
+          <t>School Readiness Preschool Program (research-based curriculum with hands-on exploration and play-based learning)</t>
+        </is>
+      </c>
+      <c r="N183" s="7" t="inlineStr"/>
+      <c r="O183" s="8" t="inlineStr">
+        <is>
+          <t>School Readiness Preschool Program; Professional Learning &amp; Curriculum department | https://www.tracy.k12.ca.us/ | 2025</t>
+        </is>
+      </c>
+      <c r="P183" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tracy.k12.ca.us/programs/preschool</t>
+        </is>
+      </c>
+      <c r="Q183" s="8" t="inlineStr">
+        <is>
+          <t>Curriculum focused on play-based, hands-on learning; half-day program offered; director contact not identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>Manteca Unified School District</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>0716310</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>San Joaquin</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>2271 East Yosemite Avenue, Manteca, CA 95336</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="inlineStr"/>
+      <c r="H184" s="3" t="inlineStr"/>
+      <c r="I184" s="3" t="inlineStr"/>
+      <c r="J184" s="3" t="inlineStr"/>
+      <c r="K184" s="3" t="inlineStr"/>
+      <c r="L184" s="3" t="inlineStr">
+        <is>
+          <t>209-825-3637</t>
+        </is>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>Universal Transitional Kindergarten (UTK) with full-day play-based learning</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
+          <t>2021-2025 (phased implementation)</t>
+        </is>
+      </c>
+      <c r="O184" s="4" t="inlineStr">
+        <is>
+          <t>Universal Transitional Kindergarten (UTK) phased implementation through 2025-26; Early Literacy Initiative (TK-3) with curriculum adoption and professional development | https://www.mantecausd.net/ | 2024</t>
+        </is>
+      </c>
+      <c r="P184" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mantecausd.net/post-details/~board/district-news/post/early-learning-matters-introducing-utk-in-musd</t>
+        </is>
+      </c>
+      <c r="Q184" s="4" t="inlineStr">
+        <is>
+          <t>UTK phased over four years; Early Literacy Initiative funded with professional development and curriculum adoption training</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="7" t="inlineStr">
+        <is>
+          <t>Contra Costa County Office of Education</t>
+        </is>
+      </c>
+      <c r="B185" s="7" t="inlineStr"/>
+      <c r="C185" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D185" s="7" t="inlineStr">
+        <is>
+          <t>Contra Costa</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="inlineStr"/>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>2500 Bisso Lane, Concord, CA 94520</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="inlineStr"/>
+      <c r="H185" s="7" t="inlineStr"/>
+      <c r="I185" s="7" t="inlineStr"/>
+      <c r="J185" s="7" t="inlineStr"/>
+      <c r="K185" s="7" t="inlineStr"/>
+      <c r="L185" s="7" t="inlineStr">
+        <is>
+          <t>925-942-3388</t>
+        </is>
+      </c>
+      <c r="M185" s="7" t="inlineStr"/>
+      <c r="N185" s="7" t="inlineStr"/>
+      <c r="O185" s="8" t="inlineStr">
+        <is>
+          <t>County-level ECE coordination | https://www.cccoe.org/ | 2025</t>
+        </is>
+      </c>
+      <c r="P185" s="7" t="inlineStr">
+        <is>
+          <t>https://www.cccoe.org/</t>
+        </is>
+      </c>
+      <c r="Q185" s="8" t="inlineStr">
+        <is>
+          <t>County Office of Education (COE) provides support to districts; contact information for ECE director not identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>Folsom-Cordova Unified School District</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>0672170</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>1965 Natoma Street, Folsom, CA 95630</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr"/>
+      <c r="H186" s="3" t="inlineStr"/>
+      <c r="I186" s="3" t="inlineStr"/>
+      <c r="J186" s="3" t="inlineStr"/>
+      <c r="K186" s="3" t="inlineStr"/>
+      <c r="L186" s="3" t="inlineStr">
+        <is>
+          <t>916-294-9000</t>
+        </is>
+      </c>
+      <c r="M186" s="3" t="inlineStr"/>
+      <c r="N186" s="3" t="inlineStr"/>
+      <c r="O186" s="4" t="inlineStr">
+        <is>
+          <t>Early childhood services offered | https://www.fcusd.org/ | 2025</t>
+        </is>
+      </c>
+      <c r="P186" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fcusd.org/</t>
+        </is>
+      </c>
+      <c r="Q186" s="4" t="inlineStr">
+        <is>
+          <t>ECE contact information not identified; recommend direct district outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t>Natomas Unified School District</t>
+        </is>
+      </c>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>0665700</t>
+        </is>
+      </c>
+      <c r="C187" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D187" s="7" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="n">
+        <v>14000</v>
+      </c>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>3901 Elkhorn Boulevard, Sacramento, CA 95842</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="inlineStr"/>
+      <c r="H187" s="7" t="inlineStr"/>
+      <c r="I187" s="7" t="inlineStr"/>
+      <c r="J187" s="7" t="inlineStr"/>
+      <c r="K187" s="7" t="inlineStr"/>
+      <c r="L187" s="7" t="inlineStr">
+        <is>
+          <t>916-567-5400</t>
+        </is>
+      </c>
+      <c r="M187" s="7" t="inlineStr"/>
+      <c r="N187" s="7" t="inlineStr"/>
+      <c r="O187" s="8" t="inlineStr">
+        <is>
+          <t>Pre-K programs offered | https://www.nusd.net/ | 2025</t>
+        </is>
+      </c>
+      <c r="P187" s="7" t="inlineStr">
+        <is>
+          <t>https://www.nusd.net/</t>
+        </is>
+      </c>
+      <c r="Q187" s="8" t="inlineStr">
+        <is>
+          <t>ECE director contact information not identified during research</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>Roseville City School District</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>0657160</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>Placer</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>1150 Elverta Road, Roseville, CA 95661</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr"/>
+      <c r="H188" s="3" t="inlineStr"/>
+      <c r="I188" s="3" t="inlineStr"/>
+      <c r="J188" s="3" t="inlineStr"/>
+      <c r="K188" s="3" t="inlineStr"/>
+      <c r="L188" s="3" t="inlineStr">
+        <is>
+          <t>916-771-1700</t>
+        </is>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>Frog Street Curriculum for Preschool and Transitional Kindergarten</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O188" s="4" t="inlineStr">
+        <is>
+          <t>Frog Street Curriculum implementation; Transitional Kindergarten (TK) with specialized curriculum | https://www.rcsdk8.org/ | 2025</t>
+        </is>
+      </c>
+      <c r="P188" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rcsdk8.org/preschool</t>
+        </is>
+      </c>
+      <c r="Q188" s="4" t="inlineStr">
+        <is>
+          <t>Frog Street Curriculum used for PreK and TK; director contact not identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="7" t="inlineStr">
+        <is>
+          <t>Rocklin Unified School District</t>
+        </is>
+      </c>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>0675560</t>
+        </is>
+      </c>
+      <c r="C189" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D189" s="7" t="inlineStr">
+        <is>
+          <t>Placer</t>
+        </is>
+      </c>
+      <c r="E189" s="7" t="n">
+        <v>13000</v>
+      </c>
+      <c r="F189" s="7" t="inlineStr">
+        <is>
+          <t>2425 Railroad Street, Rocklin, CA 95677</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="inlineStr"/>
+      <c r="H189" s="7" t="inlineStr"/>
+      <c r="I189" s="7" t="inlineStr"/>
+      <c r="J189" s="7" t="inlineStr"/>
+      <c r="K189" s="7" t="inlineStr"/>
+      <c r="L189" s="7" t="inlineStr">
+        <is>
+          <t>916-786-2400</t>
+        </is>
+      </c>
+      <c r="M189" s="7" t="inlineStr"/>
+      <c r="N189" s="7" t="inlineStr"/>
+      <c r="O189" s="8" t="inlineStr">
+        <is>
+          <t>Preschool Intervention Program (PIP); Special education preschool services | https://www.rocklinusd.org/ | 2025</t>
+        </is>
+      </c>
+      <c r="P189" s="7" t="inlineStr">
+        <is>
+          <t>https://www.rocklinusd.org/Departments/Educational-Services/Curriculum-and-Instruction/index.html</t>
+        </is>
+      </c>
+      <c r="Q189" s="8" t="inlineStr">
+        <is>
+          <t>District has Curriculum and Instruction department; specific ECE director not identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>Davis Joint Unified School District</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>0623640</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>Yolo</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>526 B Street, Davis, CA 95616</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="inlineStr"/>
+      <c r="H190" s="3" t="inlineStr"/>
+      <c r="I190" s="3" t="inlineStr"/>
+      <c r="J190" s="3" t="inlineStr"/>
+      <c r="K190" s="3" t="inlineStr"/>
+      <c r="L190" s="3" t="inlineStr">
+        <is>
+          <t>530-757-5300</t>
+        </is>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>Sobrato Early Academic Language Model (preschool through K-3), EnVision Math, Kelso's Choice (social-emotional learning)</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
+          <t>2015 (Math)</t>
+        </is>
+      </c>
+      <c r="O190" s="4" t="inlineStr">
+        <is>
+          <t>Language enrichment model for early learners; social-emotional curriculum adoption | https://www.djusd.net/ | 2025</t>
+        </is>
+      </c>
+      <c r="P190" s="3" t="inlineStr">
+        <is>
+          <t>https://www.djusd.net/instruction/curriculum/elementary_curriculum</t>
+        </is>
+      </c>
+      <c r="Q190" s="4" t="inlineStr">
+        <is>
+          <t>Comprehensive language development model starting in preschool; specific ECE director not identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="7" t="inlineStr">
+        <is>
+          <t>Woodland Joint Unified School District</t>
+        </is>
+      </c>
+      <c r="B191" s="7" t="inlineStr">
+        <is>
+          <t>0628170</t>
+        </is>
+      </c>
+      <c r="C191" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D191" s="7" t="inlineStr">
+        <is>
+          <t>Yolo</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>1475 West Main Street, Woodland, CA 95776</t>
+        </is>
+      </c>
+      <c r="G191" s="7" t="inlineStr"/>
+      <c r="H191" s="7" t="inlineStr"/>
+      <c r="I191" s="7" t="inlineStr"/>
+      <c r="J191" s="7" t="inlineStr"/>
+      <c r="K191" s="7" t="inlineStr"/>
+      <c r="L191" s="7" t="inlineStr">
+        <is>
+          <t>530-662-0201</t>
+        </is>
+      </c>
+      <c r="M191" s="7" t="inlineStr"/>
+      <c r="N191" s="7" t="inlineStr"/>
+      <c r="O191" s="8" t="inlineStr">
+        <is>
+          <t>PreK programs offered | https://www.wjusd.org/ | 2025</t>
+        </is>
+      </c>
+      <c r="P191" s="7" t="inlineStr">
+        <is>
+          <t>https://www.wjusd.org/</t>
+        </is>
+      </c>
+      <c r="Q191" s="8" t="inlineStr">
+        <is>
+          <t>ECE director contact not identified during research</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>Yuba City Unified School District</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>0745440</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>Sutter</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>1437 Plumas Street, Yuba City, CA 95991</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="inlineStr"/>
+      <c r="H192" s="3" t="inlineStr"/>
+      <c r="I192" s="3" t="inlineStr"/>
+      <c r="J192" s="3" t="inlineStr"/>
+      <c r="K192" s="3" t="inlineStr"/>
+      <c r="L192" s="3" t="inlineStr">
+        <is>
+          <t>530-822-3400</t>
+        </is>
+      </c>
+      <c r="M192" s="3" t="inlineStr"/>
+      <c r="N192" s="3" t="inlineStr"/>
+      <c r="O192" s="4" t="inlineStr">
+        <is>
+          <t>PreK programs offered | https://www.ycusd.net/ | 2025</t>
+        </is>
+      </c>
+      <c r="P192" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ycusd.net/</t>
+        </is>
+      </c>
+      <c r="Q192" s="4" t="inlineStr">
+        <is>
+          <t>ECE director contact information not identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t>Western Placer Unified School District</t>
+        </is>
+      </c>
+      <c r="B193" s="7" t="inlineStr">
+        <is>
+          <t>0651050</t>
+        </is>
+      </c>
+      <c r="C193" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D193" s="7" t="inlineStr">
+        <is>
+          <t>Placer</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F193" s="7" t="inlineStr">
+        <is>
+          <t>1259 Fruitvale Avenue, Lincoln, CA 95648</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="inlineStr"/>
+      <c r="H193" s="7" t="inlineStr"/>
+      <c r="I193" s="7" t="inlineStr"/>
+      <c r="J193" s="7" t="inlineStr"/>
+      <c r="K193" s="7" t="inlineStr"/>
+      <c r="L193" s="7" t="inlineStr">
+        <is>
+          <t>916-645-6400</t>
+        </is>
+      </c>
+      <c r="M193" s="7" t="inlineStr"/>
+      <c r="N193" s="7" t="inlineStr"/>
+      <c r="O193" s="8" t="inlineStr">
+        <is>
+          <t>Early childhood services | https://www.wpusd.org/ | 2025</t>
+        </is>
+      </c>
+      <c r="P193" s="7" t="inlineStr">
+        <is>
+          <t>https://www.wpusd.org/</t>
+        </is>
+      </c>
+      <c r="Q193" s="8" t="inlineStr">
+        <is>
+          <t>ECE director contact not publicly identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>Sacramento County Office of Education</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr"/>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr"/>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>P.O. Box 269003, Sacramento, CA 95826</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr"/>
+      <c r="H194" s="3" t="inlineStr"/>
+      <c r="I194" s="3" t="inlineStr">
+        <is>
+          <t>Executive Director, Early Learning</t>
+        </is>
+      </c>
+      <c r="J194" s="3" t="inlineStr"/>
+      <c r="K194" s="3" t="inlineStr"/>
+      <c r="L194" s="3" t="inlineStr">
+        <is>
+          <t>916-228-2506</t>
+        </is>
+      </c>
+      <c r="M194" s="3" t="inlineStr"/>
+      <c r="N194" s="3" t="inlineStr"/>
+      <c r="O194" s="4" t="inlineStr">
+        <is>
+          <t>Sacramento County Early Learning Department; County-level ECE coordination | https://www.scoe.net/ | 2025</t>
+        </is>
+      </c>
+      <c r="P194" s="3" t="inlineStr">
+        <is>
+          <t>https://sacearlylearning.org/</t>
+        </is>
+      </c>
+      <c r="Q194" s="4" t="inlineStr">
+        <is>
+          <t>County Office of Education provides ECE leadership; Executive Director position identified but name not found in public sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="7" t="inlineStr">
+        <is>
+          <t>Santa Rosa City Schools</t>
+        </is>
+      </c>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t>0704240</t>
+        </is>
+      </c>
+      <c r="C195" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D195" s="7" t="inlineStr">
+        <is>
+          <t>Sonoma</t>
+        </is>
+      </c>
+      <c r="E195" s="7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F195" s="7" t="inlineStr">
+        <is>
+          <t>211 Ridgetop Road, Santa Rosa, CA 95959</t>
+        </is>
+      </c>
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="H195" s="7" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="I195" s="7" t="inlineStr">
+        <is>
+          <t>Director, Educational Services</t>
+        </is>
+      </c>
+      <c r="J195" s="7" t="inlineStr">
+        <is>
+          <t>sysmith@srcs.k12.ca.us</t>
+        </is>
+      </c>
+      <c r="K195" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L195" s="7" t="inlineStr">
+        <is>
+          <t>707-890-3800 x80413</t>
+        </is>
+      </c>
+      <c r="M195" s="7" t="inlineStr"/>
+      <c r="N195" s="7" t="inlineStr"/>
+      <c r="O195" s="8" t="inlineStr">
+        <is>
+          <t>Educational Services and Collaborative Curriculum Design (CCD) department; early childhood curriculum oversight | https://www.srcschools.org/ | 2025</t>
+        </is>
+      </c>
+      <c r="P195" s="7" t="inlineStr">
+        <is>
+          <t>https://www.srcschools.org/site/Default.aspx?PageID=4322</t>
+        </is>
+      </c>
+      <c r="Q195" s="8" t="inlineStr">
+        <is>
+          <t>Sydney Smith is Director of Educational Services; oversees curriculum including early childhood</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>Petaluma City Schools</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>0704130</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>Sonoma</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>2220 Painters Boulevard, Petaluma, CA 94952</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="inlineStr">
+        <is>
+          <t>Gloria</t>
+        </is>
+      </c>
+      <c r="H196" s="3" t="inlineStr">
+        <is>
+          <t>Estavillo</t>
+        </is>
+      </c>
+      <c r="I196" s="3" t="inlineStr">
+        <is>
+          <t>Director, Educational Services</t>
+        </is>
+      </c>
+      <c r="J196" s="3" t="inlineStr"/>
+      <c r="K196" s="3" t="inlineStr"/>
+      <c r="L196" s="3" t="inlineStr">
+        <is>
+          <t>707-778-4600</t>
+        </is>
+      </c>
+      <c r="M196" s="3" t="inlineStr"/>
+      <c r="N196" s="3" t="inlineStr"/>
+      <c r="O196" s="4" t="inlineStr">
+        <is>
+          <t>Curriculum and Instruction department; Early Childhood Education Coordinator role | https://petalumacityschools.org/ | 2025</t>
+        </is>
+      </c>
+      <c r="P196" s="3" t="inlineStr">
+        <is>
+          <t>https://petalumacityschools.org/departments/educational-services/curriculum-instruction</t>
+        </is>
+      </c>
+      <c r="Q196" s="4" t="inlineStr">
+        <is>
+          <t>Gloria Estavillo oversees Educational Services; district has dedicated ECE Coordinator position</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="7" t="inlineStr">
+        <is>
+          <t>Windsor Unified School District</t>
+        </is>
+      </c>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t>0704600</t>
+        </is>
+      </c>
+      <c r="C197" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D197" s="7" t="inlineStr">
+        <is>
+          <t>Sonoma</t>
+        </is>
+      </c>
+      <c r="E197" s="7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F197" s="7" t="inlineStr">
+        <is>
+          <t>9010 Old Redwood Highway, Windsor, CA 95492</t>
+        </is>
+      </c>
+      <c r="G197" s="7" t="inlineStr"/>
+      <c r="H197" s="7" t="inlineStr"/>
+      <c r="I197" s="7" t="inlineStr"/>
+      <c r="J197" s="7" t="inlineStr"/>
+      <c r="K197" s="7" t="inlineStr"/>
+      <c r="L197" s="7" t="inlineStr">
+        <is>
+          <t>707-838-7215</t>
+        </is>
+      </c>
+      <c r="M197" s="7" t="inlineStr"/>
+      <c r="N197" s="7" t="inlineStr"/>
+      <c r="O197" s="8" t="inlineStr">
+        <is>
+          <t>Early childhood programs offered | https://www.wusd.org/ | 2025</t>
+        </is>
+      </c>
+      <c r="P197" s="7" t="inlineStr">
+        <is>
+          <t>https://www.wusd.org/</t>
+        </is>
+      </c>
+      <c r="Q197" s="8" t="inlineStr">
+        <is>
+          <t>ECE director contact information not publicly identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>Sonoma County Office of Education</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr"/>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>Sonoma</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr"/>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>5340 Skylane Boulevard, Santa Rosa, CA 95403</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr"/>
+      <c r="H198" s="3" t="inlineStr"/>
+      <c r="I198" s="3" t="inlineStr"/>
+      <c r="J198" s="3" t="inlineStr"/>
+      <c r="K198" s="3" t="inlineStr"/>
+      <c r="L198" s="3" t="inlineStr">
+        <is>
+          <t>707-524-2600</t>
+        </is>
+      </c>
+      <c r="M198" s="3" t="inlineStr"/>
+      <c r="N198" s="3" t="inlineStr"/>
+      <c r="O198" s="4" t="inlineStr">
+        <is>
+          <t>County-level early childhood coordination | https://www.scoe.org/ | 2025</t>
+        </is>
+      </c>
+      <c r="P198" s="3" t="inlineStr">
+        <is>
+          <t>https://www.scoe.org/</t>
+        </is>
+      </c>
+      <c r="Q198" s="4" t="inlineStr">
+        <is>
+          <t>County Office of Education; ECE director contact not identified in public sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="7" t="inlineStr">
+        <is>
+          <t>San Luis Coastal Unified School District</t>
+        </is>
+      </c>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t>0747530</t>
+        </is>
+      </c>
+      <c r="C199" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D199" s="7" t="inlineStr">
+        <is>
+          <t>San Luis Obispo</t>
+        </is>
+      </c>
+      <c r="E199" s="7" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F199" s="7" t="inlineStr">
+        <is>
+          <t>1 Mustang Drive, San Luis Obispo, CA 93405</t>
+        </is>
+      </c>
+      <c r="G199" s="7" t="inlineStr"/>
+      <c r="H199" s="7" t="inlineStr"/>
+      <c r="I199" s="7" t="inlineStr"/>
+      <c r="J199" s="7" t="inlineStr"/>
+      <c r="K199" s="7" t="inlineStr"/>
+      <c r="L199" s="7" t="inlineStr">
+        <is>
+          <t>805-546-4473</t>
+        </is>
+      </c>
+      <c r="M199" s="7" t="inlineStr">
+        <is>
+          <t>Preschool Early Education Program (PEEP) with structured play-based learning</t>
+        </is>
+      </c>
+      <c r="N199" s="7" t="inlineStr"/>
+      <c r="O199" s="8" t="inlineStr">
+        <is>
+          <t>Preschool Early Education Program (PEEP); Transitional Kindergarten (TK) program; Instructional Services Learning and Achievement (ISLA) | https://www.slcusd.org/ | 2025</t>
+        </is>
+      </c>
+      <c r="P199" s="7" t="inlineStr">
+        <is>
+          <t>https://www.slcusd.org/sss/peep</t>
+        </is>
+      </c>
+      <c r="Q199" s="8" t="inlineStr">
+        <is>
+          <t>Play-based curriculum; TK program bridges preschool to kindergarten; director contact not identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>Lucia Mar Unified School District</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>0747290</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>San Luis Obispo</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>1409 Price Street, Arroyo Grande, CA 93420</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr"/>
+      <c r="H200" s="3" t="inlineStr"/>
+      <c r="I200" s="3" t="inlineStr"/>
+      <c r="J200" s="3" t="inlineStr"/>
+      <c r="K200" s="3" t="inlineStr"/>
+      <c r="L200" s="3" t="inlineStr">
+        <is>
+          <t>805-473-2000</t>
+        </is>
+      </c>
+      <c r="M200" s="3" t="inlineStr"/>
+      <c r="N200" s="3" t="inlineStr"/>
+      <c r="O200" s="4" t="inlineStr">
+        <is>
+          <t>Early childhood programs offered | https://www.luciamarcsd.org/ | 2025</t>
+        </is>
+      </c>
+      <c r="P200" s="3" t="inlineStr">
+        <is>
+          <t>https://www.luciamarcsd.org/</t>
+        </is>
+      </c>
+      <c r="Q200" s="4" t="inlineStr">
+        <is>
+          <t>ECE director contact information not identified during research</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="7" t="inlineStr">
+        <is>
+          <t>Lompoc Unified School District</t>
+        </is>
+      </c>
+      <c r="B201" s="7" t="inlineStr">
+        <is>
+          <t>0716850</t>
+        </is>
+      </c>
+      <c r="C201" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D201" s="7" t="inlineStr">
+        <is>
+          <t>Santa Barbara</t>
+        </is>
+      </c>
+      <c r="E201" s="7" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F201" s="7" t="inlineStr">
+        <is>
+          <t>1515 East North Avenue, Lompoc, CA 93436</t>
+        </is>
+      </c>
+      <c r="G201" s="7" t="inlineStr"/>
+      <c r="H201" s="7" t="inlineStr"/>
+      <c r="I201" s="7" t="inlineStr"/>
+      <c r="J201" s="7" t="inlineStr"/>
+      <c r="K201" s="7" t="inlineStr"/>
+      <c r="L201" s="7" t="inlineStr">
+        <is>
+          <t>805-742-3200</t>
+        </is>
+      </c>
+      <c r="M201" s="7" t="inlineStr">
+        <is>
+          <t>Early Head Start, Head Start, and California State Preschool (research-based curriculum focused on whole child development)</t>
+        </is>
+      </c>
+      <c r="N201" s="7" t="inlineStr"/>
+      <c r="O201" s="8" t="inlineStr">
+        <is>
+          <t>Early Head Start (0-3), Head Start, and State Preschool programs; Whole child development focus with parenting support | https://www.lusd.org/ | 2025</t>
+        </is>
+      </c>
+      <c r="P201" s="7" t="inlineStr">
+        <is>
+          <t>https://www.lusd.org/early-childhood-education</t>
+        </is>
+      </c>
+      <c r="Q201" s="8" t="inlineStr">
+        <is>
+          <t>Multiple funding streams for ECE; Director contact not identified in public sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>Ventura County Office of Education</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr"/>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>Ventura</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr"/>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>5100 Adolfo Lopez Drive, Camarillo, CA 93010</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="inlineStr"/>
+      <c r="H202" s="3" t="inlineStr"/>
+      <c r="I202" s="3" t="inlineStr"/>
+      <c r="J202" s="3" t="inlineStr"/>
+      <c r="K202" s="3" t="inlineStr"/>
+      <c r="L202" s="3" t="inlineStr">
+        <is>
+          <t>805-383-1900</t>
+        </is>
+      </c>
+      <c r="M202" s="3" t="inlineStr"/>
+      <c r="N202" s="3" t="inlineStr"/>
+      <c r="O202" s="4" t="inlineStr">
+        <is>
+          <t>County-level ECE coordination and support | https://www.vcoe.org/ | 2025</t>
+        </is>
+      </c>
+      <c r="P202" s="3" t="inlineStr">
+        <is>
+          <t>https://www.vcoe.org/</t>
+        </is>
+      </c>
+      <c r="Q202" s="4" t="inlineStr">
+        <is>
+          <t>County Office of Education; ECE director contact not publicly identified</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:Q3"/>
   <mergeCells count="1">
